--- a/Config/xlsx/Index.xlsx
+++ b/Config/xlsx/Index.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
   <si>
     <t>模式</t>
   </si>
@@ -60,6 +60,12 @@
   </si>
   <si>
     <t>Dialogue.xlsx</t>
+  </si>
+  <si>
+    <t>CharacterData</t>
+  </si>
+  <si>
+    <t>Character.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1106,9 +1112,15 @@
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:4">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
+      <c r="A5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="6" ht="16.5" spans="1:4">
       <c r="A6" s="5"/>
